--- a/data/chapter13_augs_readtable.xlsx
+++ b/data/chapter13_augs_readtable.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyowapharma-my.sharepoint.com/personal/araya-t_kyowayakuhin_co_jp/Documents/R_scripts/R入門/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{825266EB-9986-4DC9-AAA9-721918453503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{732D8942-98B2-438C-8852-9F9CCC14D27A}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8698B7-BC75-4674-B070-2A213AA0CE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{679F564F-ACFA-4B80-A080-3905DC01ECF9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="1" xr2:uid="{679F564F-ACFA-4B80-A080-3905DC01ECF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -748,9 +743,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -788,7 +783,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -894,7 +889,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1036,7 +1031,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1045,15 +1040,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0460B82F-EC3E-4089-965A-2151E34A483D}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1081,7 +1076,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1095,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1109,7 +1104,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1123,7 +1118,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1137,7 +1132,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1151,7 +1146,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1165,7 +1160,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1179,7 +1174,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1193,7 +1188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1207,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1221,7 +1216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1235,7 +1230,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1249,7 +1244,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1263,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1291,7 +1286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1305,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1319,7 +1314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1333,7 +1328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1347,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1361,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1375,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1389,7 +1384,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1403,7 +1398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1417,7 +1412,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1434,20 +1429,21 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C18F660E-0731-4861-9C3B-58A11F0D5CDB}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="17.8984375" customWidth="1"/>
-    <col min="3" max="3" width="27.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.8984375" customWidth="1"/>
+    <col min="1" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +1457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1475,7 +1471,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1489,7 +1485,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1503,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1517,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1531,7 +1527,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1545,7 +1541,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -1559,7 +1555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1573,7 +1569,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1587,7 +1583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1601,7 +1597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>76</v>
       </c>
@@ -1615,7 +1611,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1632,5 +1628,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>